--- a/docs/data/SAP Public Cloud - Treasury Scope Item Mapping - Configurator - Base Data.xlsx
+++ b/docs/data/SAP Public Cloud - Treasury Scope Item Mapping - Configurator - Base Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanRuman\Downloads\Public Cloud\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160F0D76-8485-4358-B72A-43F6EE099FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E4E5A8-7CD9-48DD-8984-908BF245F13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
